--- a/iQRM_Class07.xlsx
+++ b/iQRM_Class07.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11010"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11020"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/GoogleDrive/My Drive/iQRM/ClassFiles/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidromoff/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E74120-BF3A-2342-85F6-4A6D9B37BC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B54495E-2B0B-0646-9D19-D9B89479B195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="28800" windowHeight="17540" tabRatio="942" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1140" yWindow="-21760" windowWidth="57000" windowHeight="17540" tabRatio="942" firstSheet="1" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today" sheetId="19" r:id="rId1"/>
@@ -30,13 +30,20 @@
     <sheet name="FinalExamReview" sheetId="17" r:id="rId15"/>
     <sheet name="ClassPolicy" sheetId="18" r:id="rId16"/>
     <sheet name="Programming" sheetId="27" r:id="rId17"/>
+    <sheet name="1" sheetId="38" r:id="rId18"/>
+    <sheet name="2" sheetId="39" r:id="rId19"/>
+    <sheet name="3" sheetId="40" r:id="rId20"/>
+    <sheet name="4" sheetId="41" r:id="rId21"/>
+    <sheet name="5" sheetId="42" r:id="rId22"/>
+    <sheet name="6" sheetId="43" r:id="rId23"/>
+    <sheet name="7" sheetId="44" r:id="rId24"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId18"/>
-    <externalReference r:id="rId19"/>
-    <externalReference r:id="rId20"/>
-    <externalReference r:id="rId21"/>
-    <externalReference r:id="rId22"/>
+    <externalReference r:id="rId25"/>
+    <externalReference r:id="rId26"/>
+    <externalReference r:id="rId27"/>
+    <externalReference r:id="rId28"/>
+    <externalReference r:id="rId29"/>
   </externalReferences>
   <definedNames>
     <definedName name="_2_10_2017" localSheetId="13">#REF!</definedName>
@@ -214,7 +221,7 @@
     <definedName name="Y" localSheetId="3">#REF!</definedName>
     <definedName name="Y">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="9.9999999999994451E-4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
@@ -235,7 +242,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="240">
   <si>
     <t>Task</t>
   </si>
@@ -1565,13 +1572,580 @@
   </si>
   <si>
     <t>Variance of Sum</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <r>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>X ~ N(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>P(X &lt; x) = ?</t>
+  </si>
+  <si>
+    <t>Represent the answer in terms of Z.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Represent the answer using the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> function.</t>
+    </r>
+  </si>
+  <si>
+    <t>P(X &lt; 6) = ?</t>
+  </si>
+  <si>
+    <t>Calculate the answer.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>X ~ N(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Y = e</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>X</t>
+    </r>
+  </si>
+  <si>
+    <t>P(Y &lt; y ) = ?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Represent the answer using the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> function.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Y ~ LN(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>P(Y &lt; y) = ?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>0</t>
+    </r>
+  </si>
+  <si>
+    <t>x̄</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ~ N(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/n)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>P(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) = ?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Accept or reject </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> = 10 at </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> = .05.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t xml:space="preserve">(-|Z|) &lt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>/2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ?</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="31">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1706,8 +2280,81 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Symbol"/>
+      <charset val="2"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Symbol"/>
+      <charset val="2"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="2"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri (Body)"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1756,6 +2403,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1775,14 +2428,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1819,13 +2473,34 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
     <cellStyle name="Followed Hyperlink" xfId="3" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="2" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="4" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 3" xfId="5" xr:uid="{ADA2F2CD-B350-D948-8506-BAEC740C2FD4}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
@@ -1896,8 +2571,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Copula3"/>
       <sheetName val="Cor_N_Cov"/>
@@ -1911,8 +2589,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="CentralLimitTheorem"/>
       <sheetName val="FnS"/>
@@ -1926,8 +2607,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Today"/>
       <sheetName val="Normal"/>
@@ -3420,8 +4104,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Today"/>
       <sheetName val="Normal"/>
@@ -3491,8 +4178,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="CreditMatrix"/>
       <sheetName val="CreditMatrix_Weighted"/>
@@ -7553,6 +8243,171 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981E9F2A-A06C-694B-854F-DE106CC26DAA}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="26"/>
+  <cols>
+    <col min="1" max="16384" width="10.83203125" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="22"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="22"/>
+      <c r="B2" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2" s="24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="27">
+      <c r="A3" s="22"/>
+      <c r="B3" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="C3" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="24"/>
+    </row>
+    <row r="5" spans="1:3" ht="29">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="22"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="C7" s="22"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="C9" s="22"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C144410-A4A6-3541-8BD8-1D0BA9378214}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="26"/>
+  <cols>
+    <col min="1" max="16384" width="10.83203125" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="22"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="22"/>
+      <c r="B2" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2" s="24">
+        <v>10</v>
+      </c>
+      <c r="D2" s="22"/>
+    </row>
+    <row r="3" spans="1:4" ht="27">
+      <c r="A3" s="22"/>
+      <c r="B3" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="C3" s="24">
+        <v>4</v>
+      </c>
+      <c r="D3" s="22"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="22"/>
+    </row>
+    <row r="5" spans="1:4" ht="29">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7166458-E2B3-654B-8BB9-509E59B382E7}">
   <sheetPr>
@@ -7670,6 +8525,540 @@
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{6CE165C1-9AA6-7741-951F-D028677B7676}"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3B9AD90-2422-8541-92D4-F1B03EE9EED6}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="26"/>
+  <cols>
+    <col min="1" max="16384" width="10.83203125" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="22"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="22"/>
+      <c r="B2" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2" s="24">
+        <v>10</v>
+      </c>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+    </row>
+    <row r="3" spans="1:5" ht="27">
+      <c r="A3" s="22"/>
+      <c r="B3" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="C3" s="24">
+        <v>4</v>
+      </c>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+    </row>
+    <row r="5" spans="1:5" ht="29">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="22"/>
+      <c r="B9" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E92A6ECE-25A8-BF4E-8EAB-123EECCC1718}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="26"/>
+  <cols>
+    <col min="1" max="16384" width="10.83203125" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="25"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="25"/>
+      <c r="B2" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2" s="27">
+        <v>10</v>
+      </c>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+    </row>
+    <row r="3" spans="1:5" ht="27">
+      <c r="A3" s="25"/>
+      <c r="B3" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="27">
+        <v>4</v>
+      </c>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+    </row>
+    <row r="5" spans="1:5" ht="29">
+      <c r="A5" s="25"/>
+      <c r="B5" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+    </row>
+    <row r="7" spans="1:5" ht="29">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="25"/>
+      <c r="B9" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="25"/>
+      <c r="B11" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62E750CF-BE4D-C348-96D7-F2EFD0874BB6}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A2:D10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="26"/>
+  <cols>
+    <col min="1" max="16384" width="10.83203125" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4">
+      <c r="A2" s="25"/>
+      <c r="B2" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2" s="27">
+        <v>10</v>
+      </c>
+      <c r="D2" s="25"/>
+    </row>
+    <row r="3" spans="1:4" ht="27">
+      <c r="A3" s="25"/>
+      <c r="B3" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="27">
+        <v>4</v>
+      </c>
+      <c r="D3" s="25"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="25"/>
+    </row>
+    <row r="5" spans="1:4" ht="29">
+      <c r="A5" s="25"/>
+      <c r="B5" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="25"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="25"/>
+      <c r="B9" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E51C93A-D5A1-F648-9D62-9B57BD6DEE25}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="26"/>
+  <cols>
+    <col min="1" max="16384" width="10.83203125" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="25"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+    </row>
+    <row r="2" spans="1:4" ht="27">
+      <c r="A2" s="25"/>
+      <c r="B2" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="C2" s="27">
+        <v>10</v>
+      </c>
+      <c r="D2" s="25"/>
+    </row>
+    <row r="3" spans="1:4" ht="27">
+      <c r="A3" s="25"/>
+      <c r="B3" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="27">
+        <v>4</v>
+      </c>
+      <c r="D3" s="25"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="25"/>
+      <c r="B4" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="27">
+        <v>6</v>
+      </c>
+      <c r="D4" s="25"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="25"/>
+      <c r="B5" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" s="27">
+        <v>16</v>
+      </c>
+      <c r="D5" s="25"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+    </row>
+    <row r="7" spans="1:4" ht="29">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+    </row>
+    <row r="9" spans="1:4" ht="31">
+      <c r="A9" s="25"/>
+      <c r="B9" s="29" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+    </row>
+    <row r="11" spans="1:4" ht="30">
+      <c r="A11" s="25"/>
+      <c r="B11" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="25"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C798F61A-A050-0845-95FF-F46E95B8A886}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A2:E13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="26"/>
+  <cols>
+    <col min="1" max="16384" width="10.83203125" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" ht="27">
+      <c r="A2" s="25"/>
+      <c r="B2" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="C2" s="27">
+        <v>10</v>
+      </c>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+    </row>
+    <row r="3" spans="1:5" ht="27">
+      <c r="A3" s="25"/>
+      <c r="B3" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="27">
+        <v>4</v>
+      </c>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="25"/>
+      <c r="B4" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="27">
+        <v>6</v>
+      </c>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="25"/>
+      <c r="B5" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" s="27">
+        <v>16</v>
+      </c>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+    </row>
+    <row r="7" spans="1:5" ht="29">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+    </row>
+    <row r="9" spans="1:5" ht="31">
+      <c r="A9" s="25"/>
+      <c r="B9" s="29" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+    </row>
+    <row r="11" spans="1:5" ht="30">
+      <c r="A11" s="25"/>
+      <c r="B11" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="25"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="25"/>
+      <c r="B13" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
